--- a/Asistente de Productividad (2).xlsx
+++ b/Asistente de Productividad (2).xlsx
@@ -3608,18 +3608,101 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3631,12 +3714,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3650,82 +3727,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3739,14 +3751,75 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3760,101 +3833,93 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3868,73 +3933,108 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3943,9 +4043,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -3954,15 +4051,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3974,95 +4064,101 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4121,10 +4217,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4154,98 +4246,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -5548,14 +5548,14 @@
     </row>
     <row r="2" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -5568,14 +5568,14 @@
     </row>
     <row r="3" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -5588,14 +5588,14 @@
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="M4" s="1"/>
@@ -5607,14 +5607,14 @@
     </row>
     <row r="5" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -5700,14 +5700,14 @@
     </row>
     <row r="10" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -5720,18 +5720,18 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="79" t="s">
+      <c r="C11" s="70"/>
+      <c r="D11" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="81"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="73"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -5764,18 +5764,18 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="79" t="s">
+      <c r="C13" s="69"/>
+      <c r="D13" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="81"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="73"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -5808,18 +5808,18 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="74"/>
-      <c r="D15" s="79" t="s">
+      <c r="C15" s="70"/>
+      <c r="D15" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="81"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="73"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -5852,18 +5852,18 @@
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="79" t="s">
+      <c r="C17" s="70"/>
+      <c r="D17" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="81"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="73"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -5896,26 +5896,26 @@
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="79" t="s">
+      <c r="C19" s="81"/>
+      <c r="D19" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="80" t="s">
+      <c r="E19" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="80" t="s">
+      <c r="F19" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="80" t="s">
+      <c r="G19" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="80" t="s">
+      <c r="H19" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="81" t="s">
+      <c r="I19" s="73" t="s">
         <v>9</v>
       </c>
       <c r="J19" s="1"/>
@@ -5992,18 +5992,18 @@
     </row>
     <row r="23" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="87" t="s">
+      <c r="B23" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="92" t="s">
+      <c r="C23" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="93"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="88"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -6016,17 +6016,17 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="88"/>
-      <c r="C24" s="69" t="str">
+      <c r="B24" s="83"/>
+      <c r="C24" s="94" t="str">
         <f>IF(D13="","",VLOOKUP(D13,Datos!$B$2:$T$7,19,0))</f>
         <v xml:space="preserve">Aterrizar la estrategia de negocio de la empresa en las tiendas de Supermercados Peruanos, con el fin de lograr el mayor número de ventas y la satisfacción máxima del consumidor. </v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="70"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="95"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -6039,14 +6039,14 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="70"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="95"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -6059,14 +6059,14 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="72"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="97"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -6099,18 +6099,18 @@
     </row>
     <row r="28" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="90" t="s">
+      <c r="C28" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="91"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="86"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -6123,16 +6123,16 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="94" t="s">
+      <c r="B29" s="83"/>
+      <c r="C29" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="94"/>
-      <c r="E29" s="94"/>
-      <c r="F29" s="94"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="95"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="90"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -6145,14 +6145,14 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="88"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="95"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="90"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -6165,14 +6165,14 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="97"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="92"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -6247,15 +6247,15 @@
     </row>
     <row r="35" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="84"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="77"/>
       <c r="I35" s="40" t="s">
         <v>17</v>
       </c>
@@ -6274,12 +6274,12 @@
       <c r="B36" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
       <c r="I36" s="38">
         <v>0.4</v>
       </c>
@@ -6295,15 +6295,15 @@
     </row>
     <row r="37" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="67" t="s">
+      <c r="B37" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="67"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
       <c r="I37" s="39">
         <v>0.15</v>
       </c>
@@ -6319,15 +6319,15 @@
     </row>
     <row r="38" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="75" t="s">
+      <c r="B38" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
+      <c r="C38" s="99"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
+      <c r="H38" s="99"/>
       <c r="I38" s="38">
         <v>0.15</v>
       </c>
@@ -6343,15 +6343,15 @@
     </row>
     <row r="39" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="100"/>
+      <c r="E39" s="100"/>
+      <c r="F39" s="100"/>
+      <c r="G39" s="100"/>
+      <c r="H39" s="100"/>
       <c r="I39" s="39">
         <v>0.1</v>
       </c>
@@ -6370,12 +6370,12 @@
       <c r="B40" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
       <c r="I40" s="38">
         <v>0.1</v>
       </c>
@@ -6391,15 +6391,15 @@
     </row>
     <row r="41" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="66" t="s">
+      <c r="B41" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
+      <c r="C41" s="74"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="74"/>
       <c r="I41" s="39">
         <v>0.1</v>
       </c>
@@ -6415,15 +6415,15 @@
     </row>
     <row r="42" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="68" t="s">
+      <c r="B42" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="79"/>
       <c r="I42" s="38">
         <v>0.05</v>
       </c>
@@ -6439,13 +6439,13 @@
     </row>
     <row r="43" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="67"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="74"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="74"/>
+      <c r="H43" s="74"/>
       <c r="I43" s="39"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -6459,13 +6459,13 @@
     </row>
     <row r="44" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
+      <c r="B44" s="79"/>
+      <c r="C44" s="79"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="79"/>
+      <c r="F44" s="79"/>
+      <c r="G44" s="79"/>
+      <c r="H44" s="79"/>
       <c r="I44" s="38">
         <v>0.05</v>
       </c>
@@ -6552,11 +6552,14 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="29">
-    <mergeCell ref="B2:I5"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="C24:I26"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:I13"/>
     <mergeCell ref="B15:C15"/>
@@ -6573,14 +6576,11 @@
     <mergeCell ref="C28:I28"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C29:I31"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="C24:I26"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B2:I5"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:I11"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:I13">
@@ -6641,15 +6641,15 @@
     </row>
     <row r="3" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="84"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="77"/>
       <c r="I3" s="42" t="s">
         <v>17</v>
       </c>
@@ -6689,15 +6689,15 @@
     </row>
     <row r="5" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
       <c r="I5" s="55">
         <v>0.05</v>
       </c>
@@ -6735,15 +6735,15 @@
     </row>
     <row r="7" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
       <c r="I7" s="55"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -6779,15 +6779,15 @@
     </row>
     <row r="9" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
       <c r="I9" s="55"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -6801,15 +6801,15 @@
     </row>
     <row r="10" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="112"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="103"/>
       <c r="I10" s="56"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -6823,15 +6823,15 @@
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
       <c r="I11" s="43">
         <f>I10+I9+I8+I7+I6+I5+I4+'1'!I44+'1'!I43+'1'!I42+'1'!I41+'1'!I40+'1'!I39+'1'!I38+'1'!I37+'1'!I36</f>
         <v>1.2000000000000002</v>
@@ -6884,79 +6884,79 @@
     </row>
     <row r="15" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="113" t="s">
+      <c r="B15" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="113"/>
-      <c r="G15" s="113"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="113"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="114"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="114"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="114"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
-      <c r="B18" s="114"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="114"/>
-      <c r="I18" s="114"/>
+      <c r="B18" s="108"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="108"/>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="114"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
-      <c r="I19" s="114"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
-      <c r="B20" s="114"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="114"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="114"/>
+      <c r="B20" s="108"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7000,78 +7000,78 @@
     </row>
     <row r="24" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="124" t="s">
+      <c r="B24" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="126"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="120"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="115" t="s">
+      <c r="B25" s="109" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="116"/>
-      <c r="I25" s="117"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="111"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="118"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="120"/>
+      <c r="B26" s="112"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="114"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="118"/>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="120"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="114"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="118"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="120"/>
+      <c r="B28" s="112"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="114"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="121"/>
-      <c r="C29" s="122"/>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="123"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="116"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="116"/>
+      <c r="I29" s="117"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
@@ -7108,16 +7108,16 @@
     </row>
     <row r="32" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="129" t="s">
+      <c r="B32" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="129"/>
-      <c r="D32" s="129"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="129"/>
-      <c r="G32" s="129"/>
-      <c r="H32" s="129"/>
-      <c r="I32" s="129"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="123"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="123"/>
+      <c r="H32" s="123"/>
+      <c r="I32" s="123"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -7125,19 +7125,19 @@
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="130" t="s">
+      <c r="B33" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="131"/>
-      <c r="D33" s="132"/>
+      <c r="C33" s="125"/>
+      <c r="D33" s="126"/>
       <c r="E33" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="F33" s="130" t="s">
+      <c r="F33" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="G33" s="131"/>
-      <c r="H33" s="132"/>
+      <c r="G33" s="125"/>
+      <c r="H33" s="126"/>
       <c r="I33" s="45" t="s">
         <v>43</v>
       </c>
@@ -7148,13 +7148,13 @@
     </row>
     <row r="34" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="107"/>
-      <c r="C34" s="108"/>
-      <c r="D34" s="109"/>
+      <c r="B34" s="127"/>
+      <c r="C34" s="128"/>
+      <c r="D34" s="129"/>
       <c r="E34" s="44"/>
-      <c r="F34" s="107"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="109"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="128"/>
+      <c r="H34" s="129"/>
       <c r="I34" s="44"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -7163,13 +7163,13 @@
     </row>
     <row r="35" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="101"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="103"/>
+      <c r="B35" s="104"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="106"/>
       <c r="E35" s="48"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="102"/>
-      <c r="H35" s="103"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="106"/>
       <c r="I35" s="48"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -7178,13 +7178,13 @@
     </row>
     <row r="36" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="107"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="109"/>
+      <c r="B36" s="127"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="129"/>
       <c r="E36" s="44"/>
-      <c r="F36" s="107"/>
-      <c r="G36" s="108"/>
-      <c r="H36" s="109"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="129"/>
       <c r="I36" s="44"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -7193,80 +7193,80 @@
     </row>
     <row r="37" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="102"/>
-      <c r="D37" s="103"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="106"/>
       <c r="E37" s="48"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="103"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="106"/>
       <c r="I37" s="48"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="107"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="109"/>
+      <c r="B38" s="127"/>
+      <c r="C38" s="128"/>
+      <c r="D38" s="129"/>
       <c r="E38" s="44"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="109"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="128"/>
+      <c r="H38" s="129"/>
       <c r="I38" s="44"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="101"/>
-      <c r="C39" s="102"/>
-      <c r="D39" s="103"/>
+      <c r="B39" s="104"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="106"/>
       <c r="E39" s="48"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="102"/>
-      <c r="H39" s="103"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="106"/>
       <c r="I39" s="48"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="107"/>
-      <c r="C40" s="108"/>
-      <c r="D40" s="109"/>
+      <c r="B40" s="127"/>
+      <c r="C40" s="128"/>
+      <c r="D40" s="129"/>
       <c r="E40" s="44"/>
-      <c r="F40" s="107"/>
-      <c r="G40" s="108"/>
-      <c r="H40" s="109"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="128"/>
+      <c r="H40" s="129"/>
       <c r="I40" s="44"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="101"/>
-      <c r="C41" s="102"/>
-      <c r="D41" s="103"/>
+      <c r="B41" s="104"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="106"/>
       <c r="E41" s="48"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="102"/>
-      <c r="H41" s="103"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="106"/>
       <c r="I41" s="48"/>
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="106" t="s">
+      <c r="B42" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
+      <c r="C42" s="130"/>
+      <c r="D42" s="130"/>
       <c r="E42" s="47">
         <f>SUM(E34:E41)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="104" t="s">
+      <c r="F42" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="G42" s="104"/>
-      <c r="H42" s="105"/>
+      <c r="G42" s="130"/>
+      <c r="H42" s="131"/>
       <c r="I42" s="46">
         <f>SUM(I34:I41)</f>
         <v>0</v>
@@ -7384,11 +7384,20 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="34">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B10:H10"/>
@@ -7404,20 +7413,11 @@
     <mergeCell ref="F33:H33"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="F34:H34"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I10">
@@ -7497,16 +7497,16 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="123" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7514,15 +7514,15 @@
       <c r="B5" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="139" t="s">
+      <c r="C5" s="156" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="139"/>
-      <c r="I5" s="139"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="156"/>
+      <c r="H5" s="156"/>
+      <c r="I5" s="156"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7542,15 +7542,15 @@
       <c r="B7" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="139" t="s">
+      <c r="C7" s="156" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="139"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
@@ -7581,54 +7581,54 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
-      <c r="B10" s="129" t="s">
+      <c r="B10" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="129"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="123"/>
+      <c r="H10" s="123"/>
+      <c r="I10" s="123"/>
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
-      <c r="B11" s="136" t="s">
+      <c r="B11" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136" t="s">
+      <c r="C11" s="157"/>
+      <c r="D11" s="157" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="136"/>
+      <c r="E11" s="157"/>
       <c r="F11" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="136" t="s">
+      <c r="G11" s="157" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="136"/>
-      <c r="I11" s="136"/>
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="154" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="137"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
+      <c r="C12" s="154"/>
+      <c r="D12" s="154"/>
+      <c r="E12" s="154"/>
       <c r="F12" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="107" t="s">
+      <c r="G12" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="108"/>
-      <c r="I12" s="109"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="129"/>
       <c r="J12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -7640,92 +7640,92 @@
     </row>
     <row r="13" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
-      <c r="B13" s="138" t="s">
+      <c r="B13" s="155" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="155"/>
+      <c r="E13" s="155"/>
       <c r="F13" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="138" t="s">
+      <c r="G13" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
+      <c r="H13" s="155"/>
+      <c r="I13" s="155"/>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
-      <c r="B14" s="137" t="s">
+      <c r="B14" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
       <c r="F14" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="107" t="s">
+      <c r="G14" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="108"/>
-      <c r="I14" s="109"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="129"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="138" t="s">
+      <c r="B15" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="155"/>
+      <c r="E15" s="155"/>
       <c r="F15" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="138" t="s">
+      <c r="G15" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="138"/>
-      <c r="I15" s="138"/>
+      <c r="H15" s="155"/>
+      <c r="I15" s="155"/>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="154" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="137"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
       <c r="F16" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="107" t="s">
+      <c r="G16" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="108"/>
-      <c r="I16" s="109"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="129"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="138" t="s">
+      <c r="B17" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="155"/>
       <c r="F17" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="138" t="s">
+      <c r="G17" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
+      <c r="H17" s="155"/>
+      <c r="I17" s="155"/>
       <c r="J17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -7737,20 +7737,20 @@
     </row>
     <row r="18" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
-      <c r="B18" s="137" t="s">
+      <c r="B18" s="154" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="137"/>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="154"/>
+      <c r="E18" s="154"/>
       <c r="F18" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="107" t="s">
+      <c r="G18" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="108"/>
-      <c r="I18" s="109"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="129"/>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7781,54 +7781,54 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="129" t="s">
+      <c r="B21" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="129"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="157" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="136"/>
-      <c r="D22" s="136" t="s">
+      <c r="C22" s="157"/>
+      <c r="D22" s="157" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="136"/>
+      <c r="E22" s="157"/>
       <c r="F22" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="136" t="s">
+      <c r="G22" s="157" t="s">
         <v>50</v>
       </c>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="157"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="137" t="s">
+      <c r="B23" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="137"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
+      <c r="C23" s="154"/>
+      <c r="D23" s="154"/>
+      <c r="E23" s="154"/>
       <c r="F23" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="G23" s="107" t="s">
+      <c r="G23" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="H23" s="108"/>
-      <c r="I23" s="109"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="129"/>
       <c r="J23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -7840,26 +7840,26 @@
     </row>
     <row r="24" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="138"/>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="138"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="155"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
       <c r="F24" s="21"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="138"/>
+      <c r="G24" s="155"/>
+      <c r="H24" s="155"/>
+      <c r="I24" s="155"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="137"/>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
+      <c r="B25" s="154"/>
+      <c r="C25" s="154"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
       <c r="F25" s="20"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="108"/>
-      <c r="I25" s="109"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="129"/>
       <c r="J25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -7871,14 +7871,14 @@
     </row>
     <row r="26" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="138"/>
+      <c r="G26" s="155"/>
+      <c r="H26" s="155"/>
+      <c r="I26" s="155"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
@@ -7909,52 +7909,52 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="129" t="s">
+      <c r="B29" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="129"/>
-      <c r="D29" s="129"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="129"/>
-      <c r="I29" s="129"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="123"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="123"/>
+      <c r="G29" s="123"/>
+      <c r="H29" s="123"/>
+      <c r="I29" s="123"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="136" t="s">
+      <c r="B30" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="136"/>
-      <c r="D30" s="136"/>
-      <c r="E30" s="136"/>
-      <c r="F30" s="136"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157"/>
+      <c r="F30" s="157"/>
       <c r="G30" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H30" s="133" t="s">
+      <c r="H30" s="135" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="133"/>
+      <c r="I30" s="135"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="137" t="s">
+      <c r="B31" s="154" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="137"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="137"/>
-      <c r="F31" s="137"/>
+      <c r="C31" s="154"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
       <c r="G31" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="134" t="s">
+      <c r="H31" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="I31" s="135"/>
+      <c r="I31" s="134"/>
       <c r="J31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -7966,32 +7966,32 @@
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="138" t="s">
+      <c r="B32" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138"/>
+      <c r="C32" s="155"/>
+      <c r="D32" s="155"/>
+      <c r="E32" s="155"/>
+      <c r="F32" s="155"/>
       <c r="G32" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="H32" s="140" t="s">
+      <c r="H32" s="151" t="s">
         <v>76</v>
       </c>
-      <c r="I32" s="141"/>
+      <c r="I32" s="137"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="137"/>
-      <c r="C33" s="137"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="137"/>
-      <c r="F33" s="137"/>
+      <c r="B33" s="154"/>
+      <c r="C33" s="154"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="154"/>
       <c r="G33" s="22"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="135"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="134"/>
       <c r="J33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -8003,14 +8003,14 @@
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="138"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
+      <c r="B34" s="155"/>
+      <c r="C34" s="155"/>
+      <c r="D34" s="155"/>
+      <c r="E34" s="155"/>
+      <c r="F34" s="155"/>
       <c r="G34" s="23"/>
-      <c r="H34" s="140"/>
-      <c r="I34" s="141"/>
+      <c r="H34" s="151"/>
+      <c r="I34" s="137"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:18" s="1" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8026,40 +8026,40 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="143" t="s">
+      <c r="B36" s="153" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="143"/>
-      <c r="D36" s="143"/>
-      <c r="E36" s="143"/>
-      <c r="F36" s="143"/>
-      <c r="G36" s="143"/>
-      <c r="H36" s="143"/>
-      <c r="I36" s="143"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="153"/>
+      <c r="H36" s="153"/>
+      <c r="I36" s="153"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="142"/>
-      <c r="C37" s="142"/>
-      <c r="D37" s="142"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="142"/>
-      <c r="I37" s="142"/>
+      <c r="B37" s="152"/>
+      <c r="C37" s="152"/>
+      <c r="D37" s="152"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="152"/>
+      <c r="H37" s="152"/>
+      <c r="I37" s="152"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="142"/>
-      <c r="C38" s="142"/>
-      <c r="D38" s="142"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142"/>
-      <c r="H38" s="142"/>
-      <c r="I38" s="142"/>
+      <c r="B38" s="152"/>
+      <c r="C38" s="152"/>
+      <c r="D38" s="152"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="152"/>
+      <c r="G38" s="152"/>
+      <c r="H38" s="152"/>
+      <c r="I38" s="152"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8090,48 +8090,48 @@
     </row>
     <row r="41" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="129" t="s">
+      <c r="B41" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="129"/>
-      <c r="D41" s="129"/>
-      <c r="E41" s="129"/>
-      <c r="F41" s="129"/>
-      <c r="G41" s="129"/>
-      <c r="H41" s="129"/>
-      <c r="I41" s="129"/>
+      <c r="C41" s="123"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="123"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="123"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="146" t="s">
+      <c r="B42" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="147"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
-      <c r="G42" s="148"/>
-      <c r="H42" s="133" t="s">
+      <c r="C42" s="139"/>
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="I42" s="133"/>
+      <c r="I42" s="135"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="149" t="s">
+      <c r="B43" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="150"/>
-      <c r="D43" s="150"/>
-      <c r="E43" s="150"/>
-      <c r="F43" s="150"/>
-      <c r="G43" s="151"/>
-      <c r="H43" s="144">
+      <c r="C43" s="142"/>
+      <c r="D43" s="142"/>
+      <c r="E43" s="142"/>
+      <c r="F43" s="142"/>
+      <c r="G43" s="143"/>
+      <c r="H43" s="133">
         <v>1</v>
       </c>
-      <c r="I43" s="135"/>
+      <c r="I43" s="134"/>
       <c r="J43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -8143,30 +8143,30 @@
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="152" t="s">
+      <c r="B44" s="144" t="s">
         <v>84</v>
       </c>
-      <c r="C44" s="153"/>
-      <c r="D44" s="153"/>
-      <c r="E44" s="153"/>
-      <c r="F44" s="153"/>
-      <c r="G44" s="154"/>
-      <c r="H44" s="145">
+      <c r="C44" s="145"/>
+      <c r="D44" s="145"/>
+      <c r="E44" s="145"/>
+      <c r="F44" s="145"/>
+      <c r="G44" s="146"/>
+      <c r="H44" s="136">
         <v>2</v>
       </c>
-      <c r="I44" s="141"/>
+      <c r="I44" s="137"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="149"/>
-      <c r="C45" s="150"/>
-      <c r="D45" s="150"/>
-      <c r="E45" s="150"/>
-      <c r="F45" s="150"/>
-      <c r="G45" s="151"/>
-      <c r="H45" s="144"/>
-      <c r="I45" s="135"/>
+      <c r="B45" s="141"/>
+      <c r="C45" s="142"/>
+      <c r="D45" s="142"/>
+      <c r="E45" s="142"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="133"/>
+      <c r="I45" s="134"/>
       <c r="J45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -8178,28 +8178,28 @@
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="155"/>
-      <c r="C46" s="156"/>
-      <c r="D46" s="156"/>
-      <c r="E46" s="156"/>
-      <c r="F46" s="156"/>
-      <c r="G46" s="157"/>
-      <c r="H46" s="145"/>
-      <c r="I46" s="141"/>
+      <c r="B46" s="147"/>
+      <c r="C46" s="148"/>
+      <c r="D46" s="148"/>
+      <c r="E46" s="148"/>
+      <c r="F46" s="148"/>
+      <c r="G46" s="149"/>
+      <c r="H46" s="136"/>
+      <c r="I46" s="137"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="129" t="s">
+      <c r="B47" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="129"/>
-      <c r="D47" s="129"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="129"/>
-      <c r="G47" s="129"/>
-      <c r="H47" s="129"/>
-      <c r="I47" s="129"/>
+      <c r="C47" s="123"/>
+      <c r="D47" s="123"/>
+      <c r="E47" s="123"/>
+      <c r="F47" s="123"/>
+      <c r="G47" s="123"/>
+      <c r="H47" s="123"/>
+      <c r="I47" s="123"/>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
@@ -8229,24 +8229,41 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="69">
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="B37:I38"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:I15"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="C7:I7"/>
@@ -8263,41 +8280,24 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="B37:I38"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
   </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:I5">
@@ -8400,18 +8400,18 @@
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="129"/>
-      <c r="K4" s="129"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8419,17 +8419,17 @@
       <c r="B5" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="196" t="s">
+      <c r="C5" s="158" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="158"/>
+      <c r="J5" s="158"/>
+      <c r="K5" s="158"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8466,9 +8466,9 @@
       <c r="H7" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="197"/>
-      <c r="J7" s="197"/>
-      <c r="K7" s="197"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="159"/>
+      <c r="K7" s="159"/>
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8502,9 +8502,9 @@
       <c r="H9" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="197"/>
-      <c r="J9" s="197"/>
-      <c r="K9" s="197"/>
+      <c r="I9" s="159"/>
+      <c r="J9" s="159"/>
+      <c r="K9" s="159"/>
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8522,60 +8522,60 @@
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
-      <c r="B11" s="165" t="s">
+      <c r="B11" s="160" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="165"/>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="165"/>
-      <c r="G11" s="165"/>
-      <c r="H11" s="165"/>
-      <c r="I11" s="165"/>
-      <c r="J11" s="165"/>
-      <c r="K11" s="165"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
       <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="161" t="s">
+      <c r="B12" s="192" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="161"/>
-      <c r="D12" s="161"/>
-      <c r="E12" s="161"/>
-      <c r="F12" s="161"/>
-      <c r="G12" s="161"/>
-      <c r="H12" s="161"/>
-      <c r="I12" s="161"/>
-      <c r="J12" s="161"/>
-      <c r="K12" s="161"/>
+      <c r="C12" s="192"/>
+      <c r="D12" s="192"/>
+      <c r="E12" s="192"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
+      <c r="I12" s="192"/>
+      <c r="J12" s="192"/>
+      <c r="K12" s="192"/>
       <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" s="1" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="162"/>
-      <c r="C13" s="162"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="162"/>
-      <c r="H13" s="162"/>
-      <c r="I13" s="162"/>
-      <c r="J13" s="162"/>
-      <c r="K13" s="162"/>
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193"/>
+      <c r="G13" s="193"/>
+      <c r="H13" s="193"/>
+      <c r="I13" s="193"/>
+      <c r="J13" s="193"/>
+      <c r="K13" s="193"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
-      <c r="B14" s="163"/>
-      <c r="C14" s="163"/>
-      <c r="D14" s="163"/>
-      <c r="E14" s="163"/>
-      <c r="F14" s="163"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="163"/>
-      <c r="I14" s="163"/>
-      <c r="J14" s="163"/>
-      <c r="K14" s="163"/>
+      <c r="B14" s="168"/>
+      <c r="C14" s="168"/>
+      <c r="D14" s="168"/>
+      <c r="E14" s="168"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="168"/>
+      <c r="H14" s="168"/>
+      <c r="I14" s="168"/>
+      <c r="J14" s="168"/>
+      <c r="K14" s="168"/>
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8593,16 +8593,16 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="163"/>
-      <c r="E16" s="163"/>
-      <c r="F16" s="163"/>
-      <c r="G16" s="163"/>
-      <c r="H16" s="163"/>
-      <c r="I16" s="163"/>
-      <c r="J16" s="163"/>
-      <c r="K16" s="163"/>
+      <c r="B16" s="168"/>
+      <c r="C16" s="168"/>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="168"/>
+      <c r="H16" s="168"/>
+      <c r="I16" s="168"/>
+      <c r="J16" s="168"/>
+      <c r="K16" s="168"/>
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8620,16 +8620,16 @@
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
-      <c r="B18" s="163"/>
-      <c r="C18" s="163"/>
-      <c r="D18" s="163"/>
-      <c r="E18" s="163"/>
-      <c r="F18" s="163"/>
-      <c r="G18" s="163"/>
-      <c r="H18" s="163"/>
-      <c r="I18" s="163"/>
-      <c r="J18" s="163"/>
-      <c r="K18" s="163"/>
+      <c r="B18" s="168"/>
+      <c r="C18" s="168"/>
+      <c r="D18" s="168"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="168"/>
+      <c r="G18" s="168"/>
+      <c r="H18" s="168"/>
+      <c r="I18" s="168"/>
+      <c r="J18" s="168"/>
+      <c r="K18" s="168"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8664,41 +8664,41 @@
     </row>
     <row r="21" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="183"/>
-      <c r="C21" s="183"/>
-      <c r="D21" s="183"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
+      <c r="B21" s="169"/>
+      <c r="C21" s="169"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
-      <c r="B22" s="184" t="s">
+      <c r="B22" s="170" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="185"/>
-      <c r="D22" s="186"/>
-      <c r="E22" s="189" t="s">
+      <c r="C22" s="171"/>
+      <c r="D22" s="172"/>
+      <c r="E22" s="175" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="190"/>
-      <c r="G22" s="191"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="190"/>
-      <c r="J22" s="190"/>
-      <c r="K22" s="192"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="176"/>
+      <c r="I22" s="176"/>
+      <c r="J22" s="176"/>
+      <c r="K22" s="178"/>
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="187"/>
-      <c r="C23" s="188"/>
-      <c r="D23" s="188"/>
+      <c r="B23" s="173"/>
+      <c r="C23" s="174"/>
+      <c r="D23" s="174"/>
       <c r="E23" s="61">
         <v>1</v>
       </c>
@@ -8711,11 +8711,11 @@
       <c r="H23" s="54">
         <v>4</v>
       </c>
-      <c r="I23" s="193">
+      <c r="I23" s="179">
         <v>5</v>
       </c>
-      <c r="J23" s="194"/>
-      <c r="K23" s="195"/>
+      <c r="J23" s="180"/>
+      <c r="K23" s="181"/>
       <c r="L23" s="34"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -8726,38 +8726,38 @@
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="171" t="s">
+      <c r="B24" s="161" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="172"/>
-      <c r="D24" s="172"/>
+      <c r="C24" s="162"/>
+      <c r="D24" s="162"/>
       <c r="E24" s="58"/>
       <c r="F24" s="63"/>
       <c r="G24" s="59"/>
       <c r="H24" s="57"/>
-      <c r="I24" s="174" t="s">
+      <c r="I24" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="J24" s="175"/>
-      <c r="K24" s="176"/>
+      <c r="J24" s="164"/>
+      <c r="K24" s="165"/>
       <c r="L24" s="35"/>
     </row>
     <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="180" t="s">
+      <c r="B25" s="166" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="181"/>
-      <c r="D25" s="181"/>
+      <c r="C25" s="167"/>
+      <c r="D25" s="167"/>
       <c r="E25" s="58"/>
       <c r="F25" s="64"/>
       <c r="G25" s="59"/>
       <c r="H25" s="57"/>
-      <c r="I25" s="174" t="s">
+      <c r="I25" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="J25" s="175"/>
-      <c r="K25" s="176"/>
+      <c r="J25" s="164"/>
+      <c r="K25" s="165"/>
       <c r="L25" s="35"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -8768,102 +8768,102 @@
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="171" t="s">
+      <c r="B26" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="172"/>
-      <c r="D26" s="173"/>
+      <c r="C26" s="162"/>
+      <c r="D26" s="182"/>
       <c r="E26" s="59"/>
       <c r="F26" s="64"/>
       <c r="G26" s="59"/>
       <c r="H26" s="57"/>
-      <c r="I26" s="174" t="s">
+      <c r="I26" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="J26" s="175"/>
-      <c r="K26" s="176"/>
+      <c r="J26" s="164"/>
+      <c r="K26" s="165"/>
       <c r="L26" s="35"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="180" t="s">
+      <c r="B27" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="181"/>
-      <c r="D27" s="181"/>
+      <c r="C27" s="167"/>
+      <c r="D27" s="167"/>
       <c r="E27" s="60"/>
       <c r="F27" s="64"/>
       <c r="G27" s="59"/>
       <c r="H27" s="57"/>
-      <c r="I27" s="174" t="s">
+      <c r="I27" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="J27" s="175"/>
-      <c r="K27" s="176"/>
+      <c r="J27" s="164"/>
+      <c r="K27" s="165"/>
       <c r="L27" s="35"/>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="171" t="s">
+      <c r="B28" s="161" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="172"/>
-      <c r="D28" s="173"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="182"/>
       <c r="E28" s="58"/>
       <c r="F28" s="64"/>
       <c r="G28" s="59"/>
       <c r="H28" s="57"/>
-      <c r="I28" s="174" t="s">
+      <c r="I28" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="J28" s="175"/>
-      <c r="K28" s="176"/>
+      <c r="J28" s="164"/>
+      <c r="K28" s="165"/>
       <c r="L28" s="35"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="180" t="s">
+      <c r="B29" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="181"/>
-      <c r="D29" s="182"/>
+      <c r="C29" s="167"/>
+      <c r="D29" s="183"/>
       <c r="E29" s="58"/>
       <c r="F29" s="64"/>
       <c r="G29" s="59"/>
       <c r="H29" s="57"/>
-      <c r="I29" s="174" t="s">
+      <c r="I29" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="J29" s="175"/>
-      <c r="K29" s="176"/>
+      <c r="J29" s="164"/>
+      <c r="K29" s="165"/>
       <c r="L29" s="35"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="171"/>
-      <c r="C30" s="172"/>
-      <c r="D30" s="173"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="162"/>
+      <c r="D30" s="182"/>
       <c r="E30" s="58"/>
       <c r="F30" s="64"/>
       <c r="G30" s="59"/>
       <c r="H30" s="57"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="176"/>
+      <c r="I30" s="163"/>
+      <c r="J30" s="164"/>
+      <c r="K30" s="165"/>
       <c r="L30" s="35"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
-      <c r="B31" s="180"/>
-      <c r="C31" s="181"/>
-      <c r="D31" s="182"/>
+      <c r="B31" s="166"/>
+      <c r="C31" s="167"/>
+      <c r="D31" s="183"/>
       <c r="E31" s="58"/>
       <c r="F31" s="64"/>
       <c r="G31" s="59"/>
       <c r="H31" s="57"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="176"/>
+      <c r="I31" s="163"/>
+      <c r="J31" s="164"/>
+      <c r="K31" s="165"/>
       <c r="L31" s="35"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -8874,30 +8874,30 @@
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="171"/>
-      <c r="C32" s="172"/>
-      <c r="D32" s="173"/>
+      <c r="B32" s="161"/>
+      <c r="C32" s="162"/>
+      <c r="D32" s="182"/>
       <c r="E32" s="58"/>
       <c r="F32" s="64"/>
       <c r="G32" s="59"/>
       <c r="H32" s="57"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="175"/>
-      <c r="K32" s="176"/>
+      <c r="I32" s="163"/>
+      <c r="J32" s="164"/>
+      <c r="K32" s="165"/>
       <c r="L32" s="35"/>
     </row>
     <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="180"/>
-      <c r="C33" s="181"/>
-      <c r="D33" s="182"/>
+      <c r="B33" s="166"/>
+      <c r="C33" s="167"/>
+      <c r="D33" s="183"/>
       <c r="E33" s="58"/>
       <c r="F33" s="64"/>
       <c r="G33" s="59"/>
       <c r="H33" s="57"/>
-      <c r="I33" s="174"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="176"/>
+      <c r="I33" s="163"/>
+      <c r="J33" s="164"/>
+      <c r="K33" s="165"/>
       <c r="L33" s="35"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -8908,42 +8908,42 @@
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="171"/>
-      <c r="C34" s="172"/>
-      <c r="D34" s="173"/>
+      <c r="B34" s="161"/>
+      <c r="C34" s="162"/>
+      <c r="D34" s="182"/>
       <c r="E34" s="58"/>
       <c r="F34" s="64"/>
       <c r="G34" s="59"/>
       <c r="H34" s="57"/>
-      <c r="I34" s="174"/>
-      <c r="J34" s="175"/>
-      <c r="K34" s="176"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="164"/>
+      <c r="K34" s="165"/>
       <c r="L34" s="35"/>
     </row>
     <row r="35" spans="1:18" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="177"/>
-      <c r="C35" s="178"/>
-      <c r="D35" s="179"/>
+      <c r="B35" s="187"/>
+      <c r="C35" s="188"/>
+      <c r="D35" s="189"/>
       <c r="E35" s="58"/>
       <c r="F35" s="65"/>
       <c r="G35" s="59"/>
       <c r="H35" s="57"/>
-      <c r="I35" s="174"/>
-      <c r="J35" s="175"/>
-      <c r="K35" s="176"/>
+      <c r="I35" s="163"/>
+      <c r="J35" s="164"/>
+      <c r="K35" s="165"/>
       <c r="L35" s="35"/>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="166"/>
-      <c r="C36" s="166"/>
-      <c r="D36" s="166"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="166"/>
-      <c r="G36" s="166"/>
-      <c r="H36" s="167"/>
-      <c r="I36" s="167"/>
+      <c r="B36" s="195"/>
+      <c r="C36" s="195"/>
+      <c r="D36" s="195"/>
+      <c r="E36" s="195"/>
+      <c r="F36" s="195"/>
+      <c r="G36" s="195"/>
+      <c r="H36" s="196"/>
+      <c r="I36" s="196"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -8959,39 +8959,39 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="168"/>
-      <c r="J37" s="168"/>
-      <c r="K37" s="168"/>
+      <c r="I37" s="197"/>
+      <c r="J37" s="197"/>
+      <c r="K37" s="197"/>
       <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:18" s="13" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12"/>
-      <c r="B38" s="169" t="s">
+      <c r="B38" s="184" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="169"/>
-      <c r="D38" s="169"/>
-      <c r="E38" s="169"/>
-      <c r="F38" s="169"/>
-      <c r="G38" s="169"/>
-      <c r="H38" s="169"/>
-      <c r="I38" s="169"/>
-      <c r="J38" s="169"/>
-      <c r="K38" s="169"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="184"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="184"/>
+      <c r="J38" s="184"/>
+      <c r="K38" s="184"/>
       <c r="L38" s="12"/>
     </row>
     <row r="39" spans="1:18" s="13" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
-      <c r="B39" s="169"/>
-      <c r="C39" s="169"/>
-      <c r="D39" s="169"/>
-      <c r="E39" s="169"/>
-      <c r="F39" s="169"/>
-      <c r="G39" s="169"/>
-      <c r="H39" s="169"/>
-      <c r="I39" s="169"/>
-      <c r="J39" s="169"/>
-      <c r="K39" s="169"/>
+      <c r="B39" s="184"/>
+      <c r="C39" s="184"/>
+      <c r="D39" s="184"/>
+      <c r="E39" s="184"/>
+      <c r="F39" s="184"/>
+      <c r="G39" s="184"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="184"/>
+      <c r="J39" s="184"/>
+      <c r="K39" s="184"/>
       <c r="L39" s="12"/>
     </row>
     <row r="40" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9002,96 +9002,96 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
-      <c r="H40" s="160"/>
-      <c r="I40" s="160"/>
+      <c r="H40" s="185"/>
+      <c r="I40" s="185"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="170" t="s">
+      <c r="B41" s="186" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="170"/>
-      <c r="D41" s="170"/>
-      <c r="E41" s="170"/>
-      <c r="F41" s="170"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="170"/>
-      <c r="I41" s="170"/>
-      <c r="J41" s="170"/>
-      <c r="K41" s="170"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="186"/>
+      <c r="E41" s="186"/>
+      <c r="F41" s="186"/>
+      <c r="G41" s="186"/>
+      <c r="H41" s="186"/>
+      <c r="I41" s="186"/>
+      <c r="J41" s="186"/>
+      <c r="K41" s="186"/>
       <c r="L41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="170"/>
-      <c r="C42" s="170"/>
-      <c r="D42" s="170"/>
-      <c r="E42" s="170"/>
-      <c r="F42" s="170"/>
-      <c r="G42" s="170"/>
-      <c r="H42" s="170"/>
-      <c r="I42" s="170"/>
-      <c r="J42" s="170"/>
-      <c r="K42" s="170"/>
+      <c r="B42" s="186"/>
+      <c r="C42" s="186"/>
+      <c r="D42" s="186"/>
+      <c r="E42" s="186"/>
+      <c r="F42" s="186"/>
+      <c r="G42" s="186"/>
+      <c r="H42" s="186"/>
+      <c r="I42" s="186"/>
+      <c r="J42" s="186"/>
+      <c r="K42" s="186"/>
       <c r="L42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="170"/>
-      <c r="C43" s="170"/>
-      <c r="D43" s="170"/>
-      <c r="E43" s="170"/>
-      <c r="F43" s="170"/>
-      <c r="G43" s="170"/>
-      <c r="H43" s="170"/>
-      <c r="I43" s="170"/>
-      <c r="J43" s="170"/>
-      <c r="K43" s="170"/>
+      <c r="B43" s="186"/>
+      <c r="C43" s="186"/>
+      <c r="D43" s="186"/>
+      <c r="E43" s="186"/>
+      <c r="F43" s="186"/>
+      <c r="G43" s="186"/>
+      <c r="H43" s="186"/>
+      <c r="I43" s="186"/>
+      <c r="J43" s="186"/>
+      <c r="K43" s="186"/>
       <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="170"/>
-      <c r="C44" s="170"/>
-      <c r="D44" s="170"/>
-      <c r="E44" s="170"/>
-      <c r="F44" s="170"/>
-      <c r="G44" s="170"/>
-      <c r="H44" s="170"/>
-      <c r="I44" s="170"/>
-      <c r="J44" s="170"/>
-      <c r="K44" s="170"/>
+      <c r="B44" s="186"/>
+      <c r="C44" s="186"/>
+      <c r="D44" s="186"/>
+      <c r="E44" s="186"/>
+      <c r="F44" s="186"/>
+      <c r="G44" s="186"/>
+      <c r="H44" s="186"/>
+      <c r="I44" s="186"/>
+      <c r="J44" s="186"/>
+      <c r="K44" s="186"/>
       <c r="L44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="170"/>
-      <c r="C45" s="170"/>
-      <c r="D45" s="170"/>
-      <c r="E45" s="170"/>
-      <c r="F45" s="170"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="170"/>
-      <c r="I45" s="170"/>
-      <c r="J45" s="170"/>
-      <c r="K45" s="170"/>
+      <c r="B45" s="186"/>
+      <c r="C45" s="186"/>
+      <c r="D45" s="186"/>
+      <c r="E45" s="186"/>
+      <c r="F45" s="186"/>
+      <c r="G45" s="186"/>
+      <c r="H45" s="186"/>
+      <c r="I45" s="186"/>
+      <c r="J45" s="186"/>
+      <c r="K45" s="186"/>
       <c r="L45" s="1"/>
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="164"/>
-      <c r="C46" s="164"/>
-      <c r="D46" s="164"/>
-      <c r="E46" s="164"/>
-      <c r="F46" s="164"/>
-      <c r="G46" s="164"/>
-      <c r="H46" s="164"/>
-      <c r="I46" s="164"/>
-      <c r="J46" s="164"/>
-      <c r="K46" s="164"/>
+      <c r="B46" s="194"/>
+      <c r="C46" s="194"/>
+      <c r="D46" s="194"/>
+      <c r="E46" s="194"/>
+      <c r="F46" s="194"/>
+      <c r="G46" s="194"/>
+      <c r="H46" s="194"/>
+      <c r="I46" s="194"/>
+      <c r="J46" s="194"/>
+      <c r="K46" s="194"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
@@ -9102,16 +9102,16 @@
     </row>
     <row r="47" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="164"/>
-      <c r="C47" s="164"/>
-      <c r="D47" s="164"/>
-      <c r="E47" s="164"/>
-      <c r="F47" s="164"/>
-      <c r="G47" s="164"/>
-      <c r="H47" s="164"/>
-      <c r="I47" s="164"/>
-      <c r="J47" s="164"/>
-      <c r="K47" s="164"/>
+      <c r="B47" s="194"/>
+      <c r="C47" s="194"/>
+      <c r="D47" s="194"/>
+      <c r="E47" s="194"/>
+      <c r="F47" s="194"/>
+      <c r="G47" s="194"/>
+      <c r="H47" s="194"/>
+      <c r="I47" s="194"/>
+      <c r="J47" s="194"/>
+      <c r="K47" s="194"/>
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -9124,8 +9124,8 @@
       <c r="E48" s="4"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="160"/>
-      <c r="I48" s="160"/>
+      <c r="H48" s="185"/>
+      <c r="I48" s="185"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -9138,14 +9138,14 @@
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
-      <c r="B49" s="159"/>
-      <c r="C49" s="159"/>
-      <c r="D49" s="159"/>
-      <c r="E49" s="159"/>
-      <c r="F49" s="159"/>
-      <c r="G49" s="159"/>
-      <c r="H49" s="160"/>
-      <c r="I49" s="160"/>
+      <c r="B49" s="191"/>
+      <c r="C49" s="191"/>
+      <c r="D49" s="191"/>
+      <c r="E49" s="191"/>
+      <c r="F49" s="191"/>
+      <c r="G49" s="191"/>
+      <c r="H49" s="185"/>
+      <c r="I49" s="185"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -9155,21 +9155,21 @@
       <c r="B50" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="158" t="s">
+      <c r="C50" s="190" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="158"/>
-      <c r="E50" s="165" t="s">
+      <c r="D50" s="190"/>
+      <c r="E50" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="F50" s="165"/>
-      <c r="G50" s="158" t="s">
+      <c r="F50" s="160"/>
+      <c r="G50" s="190" t="s">
         <v>112</v>
       </c>
-      <c r="H50" s="158"/>
-      <c r="I50" s="158"/>
-      <c r="J50" s="158"/>
-      <c r="K50" s="158"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
@@ -9183,10 +9183,10 @@
       <c r="B51" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="C51" s="158" t="s">
+      <c r="C51" s="190" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="158"/>
+      <c r="D51" s="190"/>
       <c r="E51" s="28"/>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
@@ -9198,14 +9198,14 @@
     </row>
     <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
-      <c r="B52" s="159"/>
-      <c r="C52" s="159"/>
-      <c r="D52" s="159"/>
-      <c r="E52" s="159"/>
-      <c r="F52" s="159"/>
-      <c r="G52" s="159"/>
-      <c r="H52" s="160"/>
-      <c r="I52" s="160"/>
+      <c r="B52" s="191"/>
+      <c r="C52" s="191"/>
+      <c r="D52" s="191"/>
+      <c r="E52" s="191"/>
+      <c r="F52" s="191"/>
+      <c r="G52" s="191"/>
+      <c r="H52" s="185"/>
+      <c r="I52" s="185"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -9338,44 +9338,6 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="B16:K16"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B22:D23"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="B38:K39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="B41:K45"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="I35:K35"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="H52:I52"/>
@@ -9392,6 +9354,44 @@
     <mergeCell ref="B36:G36"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="I37:K37"/>
+    <mergeCell ref="B38:K39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="B41:K45"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="B16:K16"/>
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B22:D23"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B11:K11"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50">
@@ -9443,211 +9443,211 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="198" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="241"/>
-      <c r="I2" s="241"/>
-      <c r="J2" s="242"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="200"/>
     </row>
     <row r="3" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
-      <c r="E3" s="244"/>
-      <c r="F3" s="244"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="244"/>
-      <c r="I3" s="244"/>
-      <c r="J3" s="245"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="202"/>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202"/>
+      <c r="J3" s="203"/>
     </row>
     <row r="4" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
-      <c r="H4" s="247"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="248"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="206"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="249" t="s">
+      <c r="B5" s="207" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="210" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="237"/>
-      <c r="G5" s="237"/>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="250"/>
-      <c r="C6" s="252"/>
-      <c r="D6" s="238"/>
-      <c r="E6" s="238"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
+      <c r="B6" s="208"/>
+      <c r="C6" s="212"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
+      <c r="H6" s="213"/>
+      <c r="I6" s="213"/>
+      <c r="J6" s="213"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B7" s="250"/>
-      <c r="C7" s="252"/>
-      <c r="D7" s="238"/>
-      <c r="E7" s="238"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238"/>
-      <c r="H7" s="238"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="238"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="212"/>
+      <c r="D7" s="213"/>
+      <c r="E7" s="213"/>
+      <c r="F7" s="213"/>
+      <c r="G7" s="213"/>
+      <c r="H7" s="213"/>
+      <c r="I7" s="213"/>
+      <c r="J7" s="213"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B8" s="250"/>
-      <c r="C8" s="252"/>
-      <c r="D8" s="238"/>
-      <c r="E8" s="238"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="238"/>
-      <c r="I8" s="238"/>
-      <c r="J8" s="238"/>
+      <c r="B8" s="208"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="213"/>
+      <c r="E8" s="213"/>
+      <c r="F8" s="213"/>
+      <c r="G8" s="213"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="213"/>
+      <c r="J8" s="213"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="250"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="238"/>
-      <c r="E9" s="238"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="213"/>
+      <c r="E9" s="213"/>
+      <c r="F9" s="213"/>
+      <c r="G9" s="213"/>
+      <c r="H9" s="213"/>
+      <c r="I9" s="213"/>
+      <c r="J9" s="213"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="250"/>
-      <c r="C10" s="253" t="s">
+      <c r="B10" s="208"/>
+      <c r="C10" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
+      <c r="D10" s="215"/>
+      <c r="E10" s="215"/>
+      <c r="F10" s="215"/>
+      <c r="G10" s="215"/>
+      <c r="H10" s="215"/>
+      <c r="I10" s="215"/>
+      <c r="J10" s="215"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="250"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="239"/>
-      <c r="E11" s="239"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
+      <c r="B11" s="208"/>
+      <c r="C11" s="214"/>
+      <c r="D11" s="215"/>
+      <c r="E11" s="215"/>
+      <c r="F11" s="215"/>
+      <c r="G11" s="215"/>
+      <c r="H11" s="215"/>
+      <c r="I11" s="215"/>
+      <c r="J11" s="215"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="250"/>
-      <c r="C12" s="253"/>
-      <c r="D12" s="239"/>
-      <c r="E12" s="239"/>
-      <c r="F12" s="239"/>
-      <c r="G12" s="239"/>
-      <c r="H12" s="239"/>
-      <c r="I12" s="239"/>
-      <c r="J12" s="239"/>
+      <c r="B12" s="208"/>
+      <c r="C12" s="214"/>
+      <c r="D12" s="215"/>
+      <c r="E12" s="215"/>
+      <c r="F12" s="215"/>
+      <c r="G12" s="215"/>
+      <c r="H12" s="215"/>
+      <c r="I12" s="215"/>
+      <c r="J12" s="215"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="250"/>
-      <c r="C13" s="253"/>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="239"/>
-      <c r="G13" s="239"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
+      <c r="B13" s="208"/>
+      <c r="C13" s="214"/>
+      <c r="D13" s="215"/>
+      <c r="E13" s="215"/>
+      <c r="F13" s="215"/>
+      <c r="G13" s="215"/>
+      <c r="H13" s="215"/>
+      <c r="I13" s="215"/>
+      <c r="J13" s="215"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="250"/>
-      <c r="C14" s="253"/>
-      <c r="D14" s="239"/>
-      <c r="E14" s="239"/>
-      <c r="F14" s="239"/>
-      <c r="G14" s="239"/>
-      <c r="H14" s="239"/>
-      <c r="I14" s="239"/>
-      <c r="J14" s="239"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="214"/>
+      <c r="D14" s="215"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="215"/>
+      <c r="G14" s="215"/>
+      <c r="H14" s="215"/>
+      <c r="I14" s="215"/>
+      <c r="J14" s="215"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="250"/>
-      <c r="C15" s="252" t="s">
+      <c r="B15" s="208"/>
+      <c r="C15" s="212" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="E15" s="238"/>
-      <c r="F15" s="238"/>
-      <c r="G15" s="238"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="238"/>
+      <c r="D15" s="213"/>
+      <c r="E15" s="213"/>
+      <c r="F15" s="213"/>
+      <c r="G15" s="213"/>
+      <c r="H15" s="213"/>
+      <c r="I15" s="213"/>
+      <c r="J15" s="213"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="250"/>
-      <c r="C16" s="252"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="213"/>
+      <c r="E16" s="213"/>
+      <c r="F16" s="213"/>
+      <c r="G16" s="213"/>
+      <c r="H16" s="213"/>
+      <c r="I16" s="213"/>
+      <c r="J16" s="213"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B17" s="250"/>
-      <c r="C17" s="252"/>
-      <c r="D17" s="238"/>
-      <c r="E17" s="238"/>
-      <c r="F17" s="238"/>
-      <c r="G17" s="238"/>
-      <c r="H17" s="238"/>
-      <c r="I17" s="238"/>
-      <c r="J17" s="238"/>
+      <c r="B17" s="208"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="213"/>
+      <c r="E17" s="213"/>
+      <c r="F17" s="213"/>
+      <c r="G17" s="213"/>
+      <c r="H17" s="213"/>
+      <c r="I17" s="213"/>
+      <c r="J17" s="213"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B18" s="250"/>
-      <c r="C18" s="252"/>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="238"/>
-      <c r="G18" s="238"/>
-      <c r="H18" s="238"/>
-      <c r="I18" s="238"/>
-      <c r="J18" s="238"/>
+      <c r="B18" s="208"/>
+      <c r="C18" s="212"/>
+      <c r="D18" s="213"/>
+      <c r="E18" s="213"/>
+      <c r="F18" s="213"/>
+      <c r="G18" s="213"/>
+      <c r="H18" s="213"/>
+      <c r="I18" s="213"/>
+      <c r="J18" s="213"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19" s="251"/>
-      <c r="C19" s="252"/>
-      <c r="D19" s="238"/>
-      <c r="E19" s="238"/>
-      <c r="F19" s="238"/>
-      <c r="G19" s="238"/>
-      <c r="H19" s="238"/>
-      <c r="I19" s="238"/>
-      <c r="J19" s="238"/>
+      <c r="B19" s="209"/>
+      <c r="C19" s="212"/>
+      <c r="D19" s="213"/>
+      <c r="E19" s="213"/>
+      <c r="F19" s="213"/>
+      <c r="G19" s="213"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="213"/>
+      <c r="J19" s="213"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="25"/>
@@ -9661,211 +9661,211 @@
       <c r="J20" s="24"/>
     </row>
     <row r="21" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="225" t="s">
+      <c r="C21" s="216" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="226"/>
-      <c r="I21" s="226"/>
-      <c r="J21" s="227"/>
+      <c r="D21" s="217"/>
+      <c r="E21" s="217"/>
+      <c r="F21" s="217"/>
+      <c r="G21" s="217"/>
+      <c r="H21" s="217"/>
+      <c r="I21" s="217"/>
+      <c r="J21" s="218"/>
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="228"/>
-      <c r="D22" s="229"/>
-      <c r="E22" s="229"/>
-      <c r="F22" s="229"/>
-      <c r="G22" s="229"/>
-      <c r="H22" s="229"/>
-      <c r="I22" s="229"/>
-      <c r="J22" s="230"/>
+      <c r="C22" s="219"/>
+      <c r="D22" s="220"/>
+      <c r="E22" s="220"/>
+      <c r="F22" s="220"/>
+      <c r="G22" s="220"/>
+      <c r="H22" s="220"/>
+      <c r="I22" s="220"/>
+      <c r="J22" s="221"/>
     </row>
     <row r="23" spans="2:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="231" t="s">
+      <c r="C23" s="222" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="232"/>
-      <c r="E23" s="232"/>
-      <c r="F23" s="232"/>
-      <c r="G23" s="232"/>
-      <c r="H23" s="232"/>
-      <c r="I23" s="232"/>
-      <c r="J23" s="233"/>
+      <c r="D23" s="223"/>
+      <c r="E23" s="223"/>
+      <c r="F23" s="223"/>
+      <c r="G23" s="223"/>
+      <c r="H23" s="223"/>
+      <c r="I23" s="223"/>
+      <c r="J23" s="224"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B24" s="234" t="s">
+      <c r="B24" s="225" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="237" t="s">
+      <c r="C24" s="211" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="237"/>
-      <c r="E24" s="237"/>
-      <c r="F24" s="237"/>
-      <c r="G24" s="237"/>
-      <c r="H24" s="237"/>
-      <c r="I24" s="237"/>
-      <c r="J24" s="237"/>
+      <c r="D24" s="211"/>
+      <c r="E24" s="211"/>
+      <c r="F24" s="211"/>
+      <c r="G24" s="211"/>
+      <c r="H24" s="211"/>
+      <c r="I24" s="211"/>
+      <c r="J24" s="211"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B25" s="235"/>
-      <c r="C25" s="238"/>
-      <c r="D25" s="238"/>
-      <c r="E25" s="238"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="238"/>
-      <c r="H25" s="238"/>
-      <c r="I25" s="238"/>
-      <c r="J25" s="238"/>
+      <c r="B25" s="226"/>
+      <c r="C25" s="213"/>
+      <c r="D25" s="213"/>
+      <c r="E25" s="213"/>
+      <c r="F25" s="213"/>
+      <c r="G25" s="213"/>
+      <c r="H25" s="213"/>
+      <c r="I25" s="213"/>
+      <c r="J25" s="213"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B26" s="235"/>
-      <c r="C26" s="238"/>
-      <c r="D26" s="238"/>
-      <c r="E26" s="238"/>
-      <c r="F26" s="238"/>
-      <c r="G26" s="238"/>
-      <c r="H26" s="238"/>
-      <c r="I26" s="238"/>
-      <c r="J26" s="238"/>
+      <c r="B26" s="226"/>
+      <c r="C26" s="213"/>
+      <c r="D26" s="213"/>
+      <c r="E26" s="213"/>
+      <c r="F26" s="213"/>
+      <c r="G26" s="213"/>
+      <c r="H26" s="213"/>
+      <c r="I26" s="213"/>
+      <c r="J26" s="213"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B27" s="235"/>
-      <c r="C27" s="238"/>
-      <c r="D27" s="238"/>
-      <c r="E27" s="238"/>
-      <c r="F27" s="238"/>
-      <c r="G27" s="238"/>
-      <c r="H27" s="238"/>
-      <c r="I27" s="238"/>
-      <c r="J27" s="238"/>
+      <c r="B27" s="226"/>
+      <c r="C27" s="213"/>
+      <c r="D27" s="213"/>
+      <c r="E27" s="213"/>
+      <c r="F27" s="213"/>
+      <c r="G27" s="213"/>
+      <c r="H27" s="213"/>
+      <c r="I27" s="213"/>
+      <c r="J27" s="213"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B28" s="235"/>
-      <c r="C28" s="238"/>
-      <c r="D28" s="238"/>
-      <c r="E28" s="238"/>
-      <c r="F28" s="238"/>
-      <c r="G28" s="238"/>
-      <c r="H28" s="238"/>
-      <c r="I28" s="238"/>
-      <c r="J28" s="238"/>
+      <c r="B28" s="226"/>
+      <c r="C28" s="213"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="213"/>
+      <c r="F28" s="213"/>
+      <c r="G28" s="213"/>
+      <c r="H28" s="213"/>
+      <c r="I28" s="213"/>
+      <c r="J28" s="213"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B29" s="235"/>
-      <c r="C29" s="239" t="s">
+      <c r="B29" s="226"/>
+      <c r="C29" s="215" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="239"/>
-      <c r="E29" s="239"/>
-      <c r="F29" s="239"/>
-      <c r="G29" s="239"/>
-      <c r="H29" s="239"/>
-      <c r="I29" s="239"/>
-      <c r="J29" s="239"/>
+      <c r="D29" s="215"/>
+      <c r="E29" s="215"/>
+      <c r="F29" s="215"/>
+      <c r="G29" s="215"/>
+      <c r="H29" s="215"/>
+      <c r="I29" s="215"/>
+      <c r="J29" s="215"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B30" s="235"/>
-      <c r="C30" s="239"/>
-      <c r="D30" s="239"/>
-      <c r="E30" s="239"/>
-      <c r="F30" s="239"/>
-      <c r="G30" s="239"/>
-      <c r="H30" s="239"/>
-      <c r="I30" s="239"/>
-      <c r="J30" s="239"/>
+      <c r="B30" s="226"/>
+      <c r="C30" s="215"/>
+      <c r="D30" s="215"/>
+      <c r="E30" s="215"/>
+      <c r="F30" s="215"/>
+      <c r="G30" s="215"/>
+      <c r="H30" s="215"/>
+      <c r="I30" s="215"/>
+      <c r="J30" s="215"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B31" s="235"/>
-      <c r="C31" s="239"/>
-      <c r="D31" s="239"/>
-      <c r="E31" s="239"/>
-      <c r="F31" s="239"/>
-      <c r="G31" s="239"/>
-      <c r="H31" s="239"/>
-      <c r="I31" s="239"/>
-      <c r="J31" s="239"/>
+      <c r="B31" s="226"/>
+      <c r="C31" s="215"/>
+      <c r="D31" s="215"/>
+      <c r="E31" s="215"/>
+      <c r="F31" s="215"/>
+      <c r="G31" s="215"/>
+      <c r="H31" s="215"/>
+      <c r="I31" s="215"/>
+      <c r="J31" s="215"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B32" s="235"/>
-      <c r="C32" s="239"/>
-      <c r="D32" s="239"/>
-      <c r="E32" s="239"/>
-      <c r="F32" s="239"/>
-      <c r="G32" s="239"/>
-      <c r="H32" s="239"/>
-      <c r="I32" s="239"/>
-      <c r="J32" s="239"/>
+      <c r="B32" s="226"/>
+      <c r="C32" s="215"/>
+      <c r="D32" s="215"/>
+      <c r="E32" s="215"/>
+      <c r="F32" s="215"/>
+      <c r="G32" s="215"/>
+      <c r="H32" s="215"/>
+      <c r="I32" s="215"/>
+      <c r="J32" s="215"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B33" s="235"/>
-      <c r="C33" s="239"/>
-      <c r="D33" s="239"/>
-      <c r="E33" s="239"/>
-      <c r="F33" s="239"/>
-      <c r="G33" s="239"/>
-      <c r="H33" s="239"/>
-      <c r="I33" s="239"/>
-      <c r="J33" s="239"/>
+      <c r="B33" s="226"/>
+      <c r="C33" s="215"/>
+      <c r="D33" s="215"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="215"/>
+      <c r="G33" s="215"/>
+      <c r="H33" s="215"/>
+      <c r="I33" s="215"/>
+      <c r="J33" s="215"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B34" s="235"/>
-      <c r="C34" s="238" t="s">
+      <c r="B34" s="226"/>
+      <c r="C34" s="213" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="238"/>
-      <c r="E34" s="238"/>
-      <c r="F34" s="238"/>
-      <c r="G34" s="238"/>
-      <c r="H34" s="238"/>
-      <c r="I34" s="238"/>
-      <c r="J34" s="238"/>
+      <c r="D34" s="213"/>
+      <c r="E34" s="213"/>
+      <c r="F34" s="213"/>
+      <c r="G34" s="213"/>
+      <c r="H34" s="213"/>
+      <c r="I34" s="213"/>
+      <c r="J34" s="213"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B35" s="235"/>
-      <c r="C35" s="238"/>
-      <c r="D35" s="238"/>
-      <c r="E35" s="238"/>
-      <c r="F35" s="238"/>
-      <c r="G35" s="238"/>
-      <c r="H35" s="238"/>
-      <c r="I35" s="238"/>
-      <c r="J35" s="238"/>
+      <c r="B35" s="226"/>
+      <c r="C35" s="213"/>
+      <c r="D35" s="213"/>
+      <c r="E35" s="213"/>
+      <c r="F35" s="213"/>
+      <c r="G35" s="213"/>
+      <c r="H35" s="213"/>
+      <c r="I35" s="213"/>
+      <c r="J35" s="213"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B36" s="235"/>
-      <c r="C36" s="238"/>
-      <c r="D36" s="238"/>
-      <c r="E36" s="238"/>
-      <c r="F36" s="238"/>
-      <c r="G36" s="238"/>
-      <c r="H36" s="238"/>
-      <c r="I36" s="238"/>
-      <c r="J36" s="238"/>
+      <c r="B36" s="226"/>
+      <c r="C36" s="213"/>
+      <c r="D36" s="213"/>
+      <c r="E36" s="213"/>
+      <c r="F36" s="213"/>
+      <c r="G36" s="213"/>
+      <c r="H36" s="213"/>
+      <c r="I36" s="213"/>
+      <c r="J36" s="213"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B37" s="235"/>
-      <c r="C37" s="238"/>
-      <c r="D37" s="238"/>
-      <c r="E37" s="238"/>
-      <c r="F37" s="238"/>
-      <c r="G37" s="238"/>
-      <c r="H37" s="238"/>
-      <c r="I37" s="238"/>
-      <c r="J37" s="238"/>
+      <c r="B37" s="226"/>
+      <c r="C37" s="213"/>
+      <c r="D37" s="213"/>
+      <c r="E37" s="213"/>
+      <c r="F37" s="213"/>
+      <c r="G37" s="213"/>
+      <c r="H37" s="213"/>
+      <c r="I37" s="213"/>
+      <c r="J37" s="213"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B38" s="236"/>
-      <c r="C38" s="238"/>
-      <c r="D38" s="238"/>
-      <c r="E38" s="238"/>
-      <c r="F38" s="238"/>
-      <c r="G38" s="238"/>
-      <c r="H38" s="238"/>
-      <c r="I38" s="238"/>
-      <c r="J38" s="238"/>
+      <c r="B38" s="227"/>
+      <c r="C38" s="213"/>
+      <c r="D38" s="213"/>
+      <c r="E38" s="213"/>
+      <c r="F38" s="213"/>
+      <c r="G38" s="213"/>
+      <c r="H38" s="213"/>
+      <c r="I38" s="213"/>
+      <c r="J38" s="213"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39" s="25"/>
@@ -9880,249 +9880,237 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B40" s="25"/>
-      <c r="C40" s="198" t="s">
+      <c r="C40" s="228" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="199"/>
-      <c r="E40" s="199"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="199"/>
-      <c r="I40" s="199"/>
-      <c r="J40" s="200"/>
+      <c r="D40" s="229"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="230"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="C41" s="201"/>
-      <c r="D41" s="202"/>
-      <c r="E41" s="202"/>
-      <c r="F41" s="202"/>
-      <c r="G41" s="202"/>
-      <c r="H41" s="202"/>
-      <c r="I41" s="202"/>
-      <c r="J41" s="203"/>
+      <c r="C41" s="231"/>
+      <c r="D41" s="232"/>
+      <c r="E41" s="232"/>
+      <c r="F41" s="232"/>
+      <c r="G41" s="232"/>
+      <c r="H41" s="232"/>
+      <c r="I41" s="232"/>
+      <c r="J41" s="233"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="C42" s="204" t="s">
+      <c r="C42" s="234" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="205"/>
-      <c r="E42" s="205"/>
-      <c r="F42" s="205"/>
-      <c r="G42" s="205"/>
-      <c r="H42" s="205"/>
-      <c r="I42" s="205"/>
-      <c r="J42" s="206"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
+      <c r="I42" s="235"/>
+      <c r="J42" s="236"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="C43" s="207"/>
-      <c r="D43" s="208"/>
-      <c r="E43" s="208"/>
-      <c r="F43" s="208"/>
-      <c r="G43" s="208"/>
-      <c r="H43" s="208"/>
-      <c r="I43" s="208"/>
-      <c r="J43" s="209"/>
+      <c r="C43" s="237"/>
+      <c r="D43" s="238"/>
+      <c r="E43" s="238"/>
+      <c r="F43" s="238"/>
+      <c r="G43" s="238"/>
+      <c r="H43" s="238"/>
+      <c r="I43" s="238"/>
+      <c r="J43" s="239"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B44" s="210" t="s">
+      <c r="B44" s="240" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="213" t="s">
+      <c r="C44" s="243" t="s">
         <v>127</v>
       </c>
-      <c r="D44" s="213"/>
-      <c r="E44" s="213"/>
-      <c r="F44" s="213"/>
-      <c r="G44" s="213"/>
-      <c r="H44" s="213"/>
-      <c r="I44" s="213"/>
-      <c r="J44" s="214"/>
+      <c r="D44" s="243"/>
+      <c r="E44" s="243"/>
+      <c r="F44" s="243"/>
+      <c r="G44" s="243"/>
+      <c r="H44" s="243"/>
+      <c r="I44" s="243"/>
+      <c r="J44" s="244"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B45" s="211"/>
-      <c r="C45" s="213"/>
-      <c r="D45" s="213"/>
-      <c r="E45" s="213"/>
-      <c r="F45" s="213"/>
-      <c r="G45" s="213"/>
-      <c r="H45" s="213"/>
-      <c r="I45" s="213"/>
-      <c r="J45" s="214"/>
+      <c r="B45" s="241"/>
+      <c r="C45" s="243"/>
+      <c r="D45" s="243"/>
+      <c r="E45" s="243"/>
+      <c r="F45" s="243"/>
+      <c r="G45" s="243"/>
+      <c r="H45" s="243"/>
+      <c r="I45" s="243"/>
+      <c r="J45" s="244"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B46" s="211"/>
-      <c r="C46" s="213"/>
-      <c r="D46" s="213"/>
-      <c r="E46" s="213"/>
-      <c r="F46" s="213"/>
-      <c r="G46" s="213"/>
-      <c r="H46" s="213"/>
-      <c r="I46" s="213"/>
-      <c r="J46" s="214"/>
+      <c r="B46" s="241"/>
+      <c r="C46" s="243"/>
+      <c r="D46" s="243"/>
+      <c r="E46" s="243"/>
+      <c r="F46" s="243"/>
+      <c r="G46" s="243"/>
+      <c r="H46" s="243"/>
+      <c r="I46" s="243"/>
+      <c r="J46" s="244"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B47" s="211"/>
-      <c r="C47" s="215"/>
-      <c r="D47" s="215"/>
-      <c r="E47" s="215"/>
-      <c r="F47" s="215"/>
-      <c r="G47" s="215"/>
-      <c r="H47" s="215"/>
-      <c r="I47" s="215"/>
-      <c r="J47" s="216"/>
+      <c r="B47" s="241"/>
+      <c r="C47" s="245"/>
+      <c r="D47" s="245"/>
+      <c r="E47" s="245"/>
+      <c r="F47" s="245"/>
+      <c r="G47" s="245"/>
+      <c r="H47" s="245"/>
+      <c r="I47" s="245"/>
+      <c r="J47" s="210"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B48" s="211"/>
-      <c r="C48" s="217" t="s">
+      <c r="B48" s="241"/>
+      <c r="C48" s="246" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="217"/>
-      <c r="E48" s="217"/>
-      <c r="F48" s="217"/>
-      <c r="G48" s="217"/>
-      <c r="H48" s="217"/>
-      <c r="I48" s="217"/>
-      <c r="J48" s="218"/>
+      <c r="D48" s="246"/>
+      <c r="E48" s="246"/>
+      <c r="F48" s="246"/>
+      <c r="G48" s="246"/>
+      <c r="H48" s="246"/>
+      <c r="I48" s="246"/>
+      <c r="J48" s="247"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B49" s="211"/>
-      <c r="C49" s="219"/>
-      <c r="D49" s="219"/>
-      <c r="E49" s="219"/>
-      <c r="F49" s="219"/>
-      <c r="G49" s="219"/>
-      <c r="H49" s="219"/>
-      <c r="I49" s="219"/>
-      <c r="J49" s="220"/>
+      <c r="B49" s="241"/>
+      <c r="C49" s="248"/>
+      <c r="D49" s="248"/>
+      <c r="E49" s="248"/>
+      <c r="F49" s="248"/>
+      <c r="G49" s="248"/>
+      <c r="H49" s="248"/>
+      <c r="I49" s="248"/>
+      <c r="J49" s="249"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B50" s="211"/>
-      <c r="C50" s="219"/>
-      <c r="D50" s="219"/>
-      <c r="E50" s="219"/>
-      <c r="F50" s="219"/>
-      <c r="G50" s="219"/>
-      <c r="H50" s="219"/>
-      <c r="I50" s="219"/>
-      <c r="J50" s="220"/>
+      <c r="B50" s="241"/>
+      <c r="C50" s="248"/>
+      <c r="D50" s="248"/>
+      <c r="E50" s="248"/>
+      <c r="F50" s="248"/>
+      <c r="G50" s="248"/>
+      <c r="H50" s="248"/>
+      <c r="I50" s="248"/>
+      <c r="J50" s="249"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B51" s="211"/>
-      <c r="C51" s="221"/>
-      <c r="D51" s="221"/>
-      <c r="E51" s="221"/>
-      <c r="F51" s="221"/>
-      <c r="G51" s="221"/>
-      <c r="H51" s="221"/>
-      <c r="I51" s="221"/>
-      <c r="J51" s="222"/>
+      <c r="B51" s="241"/>
+      <c r="C51" s="250"/>
+      <c r="D51" s="250"/>
+      <c r="E51" s="250"/>
+      <c r="F51" s="250"/>
+      <c r="G51" s="250"/>
+      <c r="H51" s="250"/>
+      <c r="I51" s="250"/>
+      <c r="J51" s="251"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B52" s="211"/>
-      <c r="C52" s="223" t="s">
+      <c r="B52" s="241"/>
+      <c r="C52" s="252" t="s">
         <v>129</v>
       </c>
-      <c r="D52" s="223"/>
-      <c r="E52" s="223"/>
-      <c r="F52" s="223"/>
-      <c r="G52" s="223"/>
-      <c r="H52" s="223"/>
-      <c r="I52" s="223"/>
-      <c r="J52" s="224"/>
+      <c r="D52" s="252"/>
+      <c r="E52" s="252"/>
+      <c r="F52" s="252"/>
+      <c r="G52" s="252"/>
+      <c r="H52" s="252"/>
+      <c r="I52" s="252"/>
+      <c r="J52" s="253"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B53" s="211"/>
-      <c r="C53" s="213"/>
-      <c r="D53" s="213"/>
-      <c r="E53" s="213"/>
-      <c r="F53" s="213"/>
-      <c r="G53" s="213"/>
-      <c r="H53" s="213"/>
-      <c r="I53" s="213"/>
-      <c r="J53" s="214"/>
+      <c r="B53" s="241"/>
+      <c r="C53" s="243"/>
+      <c r="D53" s="243"/>
+      <c r="E53" s="243"/>
+      <c r="F53" s="243"/>
+      <c r="G53" s="243"/>
+      <c r="H53" s="243"/>
+      <c r="I53" s="243"/>
+      <c r="J53" s="244"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B54" s="211"/>
-      <c r="C54" s="213"/>
-      <c r="D54" s="213"/>
-      <c r="E54" s="213"/>
-      <c r="F54" s="213"/>
-      <c r="G54" s="213"/>
-      <c r="H54" s="213"/>
-      <c r="I54" s="213"/>
-      <c r="J54" s="214"/>
+      <c r="B54" s="241"/>
+      <c r="C54" s="243"/>
+      <c r="D54" s="243"/>
+      <c r="E54" s="243"/>
+      <c r="F54" s="243"/>
+      <c r="G54" s="243"/>
+      <c r="H54" s="243"/>
+      <c r="I54" s="243"/>
+      <c r="J54" s="244"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B55" s="211"/>
-      <c r="C55" s="215"/>
-      <c r="D55" s="215"/>
-      <c r="E55" s="215"/>
-      <c r="F55" s="215"/>
-      <c r="G55" s="215"/>
-      <c r="H55" s="215"/>
-      <c r="I55" s="215"/>
-      <c r="J55" s="216"/>
+      <c r="B55" s="241"/>
+      <c r="C55" s="245"/>
+      <c r="D55" s="245"/>
+      <c r="E55" s="245"/>
+      <c r="F55" s="245"/>
+      <c r="G55" s="245"/>
+      <c r="H55" s="245"/>
+      <c r="I55" s="245"/>
+      <c r="J55" s="210"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B56" s="211"/>
-      <c r="C56" s="217" t="s">
+      <c r="B56" s="241"/>
+      <c r="C56" s="246" t="s">
         <v>130</v>
       </c>
-      <c r="D56" s="217"/>
-      <c r="E56" s="217"/>
-      <c r="F56" s="217"/>
-      <c r="G56" s="217"/>
-      <c r="H56" s="217"/>
-      <c r="I56" s="217"/>
-      <c r="J56" s="218"/>
+      <c r="D56" s="246"/>
+      <c r="E56" s="246"/>
+      <c r="F56" s="246"/>
+      <c r="G56" s="246"/>
+      <c r="H56" s="246"/>
+      <c r="I56" s="246"/>
+      <c r="J56" s="247"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B57" s="211"/>
-      <c r="C57" s="219"/>
-      <c r="D57" s="219"/>
-      <c r="E57" s="219"/>
-      <c r="F57" s="219"/>
-      <c r="G57" s="219"/>
-      <c r="H57" s="219"/>
-      <c r="I57" s="219"/>
-      <c r="J57" s="220"/>
+      <c r="B57" s="241"/>
+      <c r="C57" s="248"/>
+      <c r="D57" s="248"/>
+      <c r="E57" s="248"/>
+      <c r="F57" s="248"/>
+      <c r="G57" s="248"/>
+      <c r="H57" s="248"/>
+      <c r="I57" s="248"/>
+      <c r="J57" s="249"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B58" s="211"/>
-      <c r="C58" s="219"/>
-      <c r="D58" s="219"/>
-      <c r="E58" s="219"/>
-      <c r="F58" s="219"/>
-      <c r="G58" s="219"/>
-      <c r="H58" s="219"/>
-      <c r="I58" s="219"/>
-      <c r="J58" s="220"/>
+      <c r="B58" s="241"/>
+      <c r="C58" s="248"/>
+      <c r="D58" s="248"/>
+      <c r="E58" s="248"/>
+      <c r="F58" s="248"/>
+      <c r="G58" s="248"/>
+      <c r="H58" s="248"/>
+      <c r="I58" s="248"/>
+      <c r="J58" s="249"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B59" s="212"/>
-      <c r="C59" s="221"/>
-      <c r="D59" s="221"/>
-      <c r="E59" s="221"/>
-      <c r="F59" s="221"/>
-      <c r="G59" s="221"/>
-      <c r="H59" s="221"/>
-      <c r="I59" s="221"/>
-      <c r="J59" s="222"/>
+      <c r="B59" s="242"/>
+      <c r="C59" s="250"/>
+      <c r="D59" s="250"/>
+      <c r="E59" s="250"/>
+      <c r="F59" s="250"/>
+      <c r="G59" s="250"/>
+      <c r="H59" s="250"/>
+      <c r="I59" s="250"/>
+      <c r="J59" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C2:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="B5:B19"/>
-    <mergeCell ref="C5:J9"/>
-    <mergeCell ref="C10:J14"/>
-    <mergeCell ref="C15:J19"/>
-    <mergeCell ref="C21:J22"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="B24:B38"/>
-    <mergeCell ref="C24:J28"/>
-    <mergeCell ref="C29:J33"/>
-    <mergeCell ref="C34:J38"/>
     <mergeCell ref="C40:J41"/>
     <mergeCell ref="C42:J43"/>
     <mergeCell ref="B44:B59"/>
@@ -10130,6 +10118,18 @@
     <mergeCell ref="C48:J51"/>
     <mergeCell ref="C52:J55"/>
     <mergeCell ref="C56:J59"/>
+    <mergeCell ref="C21:J22"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="B24:B38"/>
+    <mergeCell ref="C24:J28"/>
+    <mergeCell ref="C29:J33"/>
+    <mergeCell ref="C34:J38"/>
+    <mergeCell ref="C2:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="B5:B19"/>
+    <mergeCell ref="C5:J9"/>
+    <mergeCell ref="C10:J14"/>
+    <mergeCell ref="C15:J19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21582,6 +21582,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010037C40AD090E3A84186D7BBB88C31AF3C" ma:contentTypeVersion="6" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="7e1abd71597409969baad51c444159f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1533ca8c-1358-4ffe-bdd8-76054b84d919" xmlns:ns3="6e7fc052-9f5f-42a4-9d28-f5df784341e4" xmlns:ns4="4d2d4251-b4c2-4310-ae5b-70569da2d9b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="78695aaddd72c4b8fffcff6aa5ad7b46" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="1533ca8c-1358-4ffe-bdd8-76054b84d919"/>
@@ -21829,15 +21838,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -21849,6 +21849,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6B8D50A-AAD5-4E29-A2DF-1FE5D99FAE69}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A46B65D-BE0B-4284-A070-C7AA5D9DD5BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21864,14 +21872,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6B8D50A-AAD5-4E29-A2DF-1FE5D99FAE69}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
